--- a/feedback_surveys/024_payroll_helpdesk_experience_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/024_payroll_helpdesk_experience_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -696,397 +696,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>feedback_email</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Would you like to provide a feedback email?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>feedback_phone</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Would you like to provide a feedback phone number?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>feedback_comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>response_time</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>How long it takes for your request to be responded to?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>professionalism</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How professional were the staff you interacted with?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>issue_resolution</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How well was your issue resolved?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Do you have any additional comments or suggestions?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Who was assigned to support your request?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>feedback_email</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Would you like to provide a feedback email?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>feedback_phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Would you like to provide a feedback phone number?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>feedback_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>response_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How long it takes for your request to be responded to?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>professionalism</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How professional were the staff you interacted with?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>issue_resolution</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How well was your issue resolved?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any additional comments or suggestions?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Who was assigned to support your request?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>feedback_email</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Would you like to provide a feedback email?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1098,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1305,380 +914,6 @@
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>extremely_professional</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Extremely Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>somewhat_professional</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Somewhat Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>not_very_professional</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Not Very Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>not_at_all_professional</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Not at All Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fully_resolved</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fully Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>partially_resolved</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Partially Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>not_resolved</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Not Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>hr_team_member</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>HR Team Member</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>payroll_team_member</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Payroll Team Member</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>extremely_professional</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Extremely Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>somewhat_professional</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Somewhat Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>not_very_professional</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Not Very Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>professionalism_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>not_at_all_professional</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Not at All Professional</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fully_resolved</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fully Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>partially_resolved</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Partially Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>not_resolved</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not Resolved</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>issue_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>hr_team_member</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HR Team Member</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>payroll_team_member</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Payroll Team Member</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
